--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1487.87</v>
+        <v>1468.64</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8486.07</v>
+        <v>8376.389999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1122.56</v>
+        <v>1108.05</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4218.94</v>
+        <v>4164.41</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1440.86</v>
+        <v>1422.24</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>35685.86</v>
+        <v>35224.59</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6079.94</v>
+        <v>6001.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2140.32</v>
+        <v>2112.66</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2737.36</v>
+        <v>2701.98</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4935.8</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3861.93</v>
+        <v>3812.01</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7499.15</v>
+        <v>7403.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10740.45</v>
+        <v>10604.02</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10916.5</v>
+        <v>10777.84</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>808.23</v>
+        <v>797.96</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3136.34</v>
+        <v>3096.5</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8052.18</v>
+        <v>7949.9</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12313.32</v>
+        <v>12156.91</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26538.6</v>
+        <v>26201.51</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3073.19</v>
+        <v>3034.15</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26835.32</v>
+        <v>26494.45</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>929.37</v>
+        <v>917.5700000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1085.94</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>801.6900000000001</v>
+        <v>791.5</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3031.28</v>
+        <v>2992.77</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1053.4</v>
+        <v>1040.02</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2153.21</v>
+        <v>2125.86</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2785.25</v>
+        <v>2749.87</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4126.47</v>
+        <v>4074.06</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1333.84</v>
+        <v>1316.9</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>16110.67</v>
+        <v>15906.03</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9493.41</v>
+        <v>9398.959999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1072.32</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7749.53</v>
+        <v>7672.42</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1198.3</v>
+        <v>1186.37</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9131.93</v>
+        <v>9041.07</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4096.03</v>
+        <v>4055.28</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2000.48</v>
+        <v>1980.58</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3717.99</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>27899.31</v>
+        <v>27621.72</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4370.23</v>
+        <v>4326.75</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>42297.97</v>
+        <v>41877.12</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1885.45</v>
+        <v>1866.69</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3604.75</v>
+        <v>3568.89</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7361.87</v>
+        <v>7288.62</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>760.58</v>
+        <v>753.01</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>59369.11</v>
+        <v>58778.41</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>102325.45</v>
+        <v>101307.36</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>15084.51</v>
+        <v>14934.43</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2677.55</v>
+        <v>2650.91</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6653.43</v>
+        <v>6587.23</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3480.75</v>
+        <v>3446.12</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1069.81</v>
+        <v>1059.17</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2877.31</v>
+        <v>2848.69</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2227.54</v>
+        <v>2205.38</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>9088.75</v>
+        <v>8998.32</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1462.88</v>
+        <v>1448.33</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3564.07</v>
+        <v>3528.6</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1046.14</v>
+        <v>1035.73</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5154.29</v>
+        <v>5103.01</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>819.74</v>
+        <v>811.58</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1616.33</v>
+        <v>1600.25</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1042.97</v>
+        <v>1039.23</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3538.22</v>
+        <v>3525.54</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>958.17</v>
+        <v>954.73</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1914.82</v>
+        <v>1907.96</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14104.75</v>
+        <v>14054.17</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3794.59</v>
+        <v>3780.99</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8310.9</v>
+        <v>8281.1</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1894.02</v>
+        <v>1887.23</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1541.5</v>
+        <v>1535.98</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1737.25</v>
+        <v>1731.02</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1374.2</v>
+        <v>1369.27</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7853.03</v>
+        <v>7824.87</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3250.08</v>
+        <v>3238.43</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4994.77</v>
+        <v>4976.86</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3787.79</v>
+        <v>3774.2</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2074.25</v>
+        <v>2066.81</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2653.64</v>
+        <v>2644.13</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>12473.5</v>
+        <v>12428.77</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1757.01</v>
+        <v>1750.71</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5576.15</v>
+        <v>5556.15</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8413.73</v>
+        <v>8383.559999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>771.6799999999999</v>
+        <v>768.92</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2514.62</v>
+        <v>2505.6</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3164.65</v>
+        <v>3157.8</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14300.3</v>
+        <v>14269.35</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3156.95</v>
+        <v>3150.11</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>16755</v>
+        <v>16718.74</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1617.27</v>
+        <v>1613.77</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5378.89</v>
+        <v>5367.25</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1262.47</v>
+        <v>1259.74</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>14136.12</v>
+        <v>14105.53</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>34326.94</v>
+        <v>34252.65</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>767.03</v>
+        <v>765.37</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2766.47</v>
+        <v>2760.48</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1745.47</v>
+        <v>1741.69</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1001.73</v>
+        <v>999.5700000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>964.9400000000001</v>
+        <v>962.85</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1944.86</v>
+        <v>1940.66</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2330.19</v>
+        <v>2325.14</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3949.76</v>
+        <v>3941.22</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13043.6</v>
+        <v>12988.92</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>23085.86</v>
+        <v>22989.07</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2339.7</v>
+        <v>2329.89</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2724.63</v>
+        <v>2713.21</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>33828.92</v>
+        <v>33687.1</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7607.82</v>
+        <v>7575.92</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3136.52</v>
+        <v>3123.37</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>789.7</v>
+        <v>786.39</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3457.75</v>
+        <v>3443.26</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2955.33</v>
+        <v>2942.94</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2949.43</v>
+        <v>2937.06</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5337.47</v>
+        <v>5315.1</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1075.11</v>
+        <v>1070.6</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1247.51</v>
+        <v>1242.28</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1262.43</v>
+        <v>1257.13</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1700.9</v>
+        <v>1681.22</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>808.23</v>
+        <v>798.87</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>41750.21</v>
+        <v>41267.03</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9168.67</v>
+        <v>9062.559999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>18402.3</v>
+        <v>18189.33</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>50501.06</v>
+        <v>49916.6</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1685.97</v>
+        <v>1666.45</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8408.299999999999</v>
+        <v>8310.99</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1467.62</v>
+        <v>1450.64</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>7060.06</v>
+        <v>6978.35</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>761.42</v>
+        <v>752.61</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1186.96</v>
+        <v>1173.22</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>27506.02</v>
+        <v>27187.69</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1153.74</v>
+        <v>1140.39</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7422.26</v>
+        <v>7336.36</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2369.58</v>
+        <v>2342.15</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>923.02</v>
+        <v>912.34</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4510.91</v>
+        <v>4458.7</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2647.51</v>
+        <v>2616.87</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9098.370000000001</v>
+        <v>8993.08</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7498.98</v>
+        <v>7435.46</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>12327.55</v>
+        <v>12223.13</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>880.65</v>
+        <v>873.1900000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>9494.879999999999</v>
+        <v>9414.450000000001</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1034.42</v>
+        <v>1025.66</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>24542.47</v>
+        <v>24334.57</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2075.56</v>
+        <v>2057.98</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1006.23</v>
+        <v>997.71</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5997.97</v>
+        <v>5947.17</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2666.16</v>
+        <v>2643.58</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4866.38</v>
+        <v>4825.15</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>31467.68</v>
+        <v>31201.12</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5179.28</v>
+        <v>5135.41</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1543.97</v>
+        <v>1530.89</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2826.27</v>
+        <v>2802.33</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5296.8</v>
+        <v>5251.94</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>760.03</v>
+        <v>753.6</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2623.57</v>
+        <v>2601.34</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1512.87</v>
+        <v>1500.05</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13656.67</v>
+        <v>13540.98</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>45833.58</v>
+        <v>45796.74</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>11630.94</v>
+        <v>11621.59</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>72933.34</v>
+        <v>72874.72</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1972.5</v>
+        <v>1970.92</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1058.99</v>
+        <v>1058.14</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1820.42</v>
+        <v>1818.95</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>7006.17</v>
+        <v>7000.54</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6128.19</v>
+        <v>6123.26</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3918.45</v>
+        <v>3915.3</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>14684.66</v>
+        <v>14672.85</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>19035.66</v>
+        <v>19020.36</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>22389.57</v>
+        <v>22371.57</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8822.1</v>
+        <v>8815.01</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2900.67</v>
+        <v>2898.34</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5965.18</v>
+        <v>5960.38</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1531.58</v>
+        <v>1530.35</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>8055.01</v>
+        <v>8048.54</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>27275.35</v>
+        <v>27253.43</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>11480.81</v>
+        <v>11471.58</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2182.79</v>
+        <v>2181.04</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7287.04</v>
+        <v>7281.18</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1847.65</v>
+        <v>1846.16</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3522</v>
+        <v>3519.17</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>75643.45</v>
+        <v>75582.64999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3127.99</v>
+        <v>3125.48</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>17540.39</v>
+        <v>17526.29</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1726.32</v>
+        <v>1724.93</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>800.62</v>
+        <v>799.98</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>18058.41</v>
+        <v>18043.89</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8240</v>
+        <v>8233.379999999999</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2263.54</v>
+        <v>2261.72</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>21582.97</v>
+        <v>21665.81</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1149.13</v>
+        <v>1153.54</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3419.12</v>
+        <v>3432.24</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6384.52</v>
+        <v>6409.02</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3087.67</v>
+        <v>3099.52</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3255.63</v>
+        <v>3268.12</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3162.27</v>
+        <v>3174.4</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>73226.53</v>
+        <v>73507.59</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1032.88</v>
+        <v>1036.85</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>769.5</v>
+        <v>772.46</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>70512.69</v>
+        <v>70783.33</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1233.2</v>
+        <v>1237.94</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1349.25</v>
+        <v>1354.43</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5857.71</v>
+        <v>5880.2</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3467.31</v>
+        <v>3480.61</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1408</v>
+        <v>1413.4</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3063.41</v>
+        <v>3075.17</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2005.97</v>
+        <v>2015.06</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>22971.08</v>
+        <v>23075.18</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3364.14</v>
+        <v>3379.38</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>22523.43</v>
+        <v>22625.5</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>11598.33</v>
+        <v>11650.89</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>4204.52</v>
+        <v>4223.58</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2641.15</v>
+        <v>2653.12</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3131.74</v>
+        <v>3145.93</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>908.1900000000001</v>
+        <v>912.3</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3536.97</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2647.15</v>
+        <v>2659.14</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>806.59</v>
+        <v>810.24</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>9536.459999999999</v>
+        <v>9579.68</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>19032.46</v>
+        <v>19118.7</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>50599.1</v>
+        <v>50828.4</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3154.58</v>
+        <v>3168.88</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>6826.99</v>
+        <v>6857.93</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>21070.68</v>
+        <v>21166.17</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>871.12</v>
+        <v>875.0700000000001</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>21812.7</v>
+        <v>21911.55</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7130.94</v>
+        <v>7163.25</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1684.67</v>
+        <v>1692.3</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>11758.43</v>
+        <v>11811.71</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>927.78</v>
+        <v>931.99</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1850.38</v>
+        <v>1858.76</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4286.28</v>
+        <v>4305.7</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1090.33</v>
+        <v>1093.22</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>857.27</v>
+        <v>859.54</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2731.54</v>
+        <v>2738.78</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1472.44</v>
+        <v>1476.35</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3623.18</v>
+        <v>3632.79</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6548.98</v>
+        <v>6566.35</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>59760.75</v>
+        <v>59919.22</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>10951.29</v>
+        <v>10980.33</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>67867.28999999999</v>
+        <v>68047.25999999999</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1453.34</v>
+        <v>1457.2</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>849.48</v>
+        <v>851.73</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>16039.76</v>
+        <v>16082.3</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>12495.29</v>
+        <v>12528.43</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>9263</v>
+        <v>9287.559999999999</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5264.25</v>
+        <v>5278.21</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1191.81</v>
+        <v>1194.97</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>18026.45</v>
+        <v>18074.26</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4219.06</v>
+        <v>4230.25</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>13429.67</v>
+        <v>13465.28</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1041.24</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>13351.94</v>
+        <v>13387.34</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>12497.34</v>
+        <v>12530.48</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>8169.49</v>
+        <v>8158.03</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3241.22</v>
+        <v>3236.67</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2763.72</v>
+        <v>2759.84</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>10545.98</v>
+        <v>10531.18</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>893.59</v>
+        <v>892.33</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1351.84</v>
+        <v>1349.94</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2448.42</v>
+        <v>2444.98</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>41526.15</v>
+        <v>41467.9</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2943.3</v>
+        <v>2939.17</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3832.69</v>
+        <v>3827.31</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2115.37</v>
+        <v>2112.4</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6382.25</v>
+        <v>6373.3</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3760.75</v>
+        <v>3755.47</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>850.48</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4021.02</v>
+        <v>4026.18</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>52024.57</v>
+        <v>52091.27</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1484.95</v>
+        <v>1486.85</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3457.9</v>
+        <v>3462.33</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>7898.14</v>
+        <v>7908.26</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3537.98</v>
+        <v>3542.52</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>911.1799999999999</v>
+        <v>912.35</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1010.01</v>
+        <v>1011.3</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>17781.27</v>
+        <v>17804.06</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>6742.05</v>
+        <v>6750.69</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3895.88</v>
+        <v>3900.88</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>51183.94</v>
+        <v>51249.56</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2640.13</v>
+        <v>2643.51</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>16442.28</v>
+        <v>16463.35</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1562.38</v>
+        <v>1564.38</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4034.32</v>
+        <v>4039.49</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3826.97</v>
+        <v>3831.88</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5683.58</v>
+        <v>5690.87</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2807.69</v>
+        <v>2811.29</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>22266.78</v>
+        <v>22420.05</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>5813.86</v>
+        <v>5853.87</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>5201.69</v>
+        <v>5237.49</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>4817.86</v>
+        <v>4851.03</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>793.28</v>
+        <v>798.74</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>7831.95</v>
+        <v>7885.85</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>964.4299999999999</v>
+        <v>971.0700000000001</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3446.59</v>
+        <v>3470.31</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>815.59</v>
+        <v>821.21</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2256.48</v>
+        <v>2272.01</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2549.12</v>
+        <v>2566.67</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2639.36</v>
+        <v>2657.52</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>975.09</v>
+        <v>981.8</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2314.73</v>
+        <v>2330.67</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3539.68</v>
+        <v>3564.04</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>30098.27</v>
+        <v>30305.44</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1172.64</v>
+        <v>1180.71</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>68700.12</v>
+        <v>69172.99000000001</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3300.31</v>
+        <v>3323.02</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1976.92</v>
+        <v>1993.81</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1135.88</v>
+        <v>1145.59</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1291.1</v>
+        <v>1302.14</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1085.88</v>
+        <v>1095.16</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2438.68</v>
+        <v>2459.52</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>12102.95</v>
+        <v>12206.38</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1126.71</v>
+        <v>1136.34</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>7856.74</v>
+        <v>7923.89</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1309.25</v>
+        <v>1320.44</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>5447.93</v>
+        <v>5494.49</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>5673.58</v>
+        <v>5722.06</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>786.66</v>
+        <v>793.39</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1238.76</v>
+        <v>1249.34</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1375.3</v>
+        <v>1387.05</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5244.61</v>
+        <v>5289.43</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>5170.22</v>
+        <v>5214.4</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>8416.92</v>
+        <v>8488.85</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4763.99</v>
+        <v>4804.7</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>900.78</v>
+        <v>908.48</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>991.39</v>
+        <v>1002.02</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3816.15</v>
+        <v>3857.09</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>9351.059999999999</v>
+        <v>9451.360000000001</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1613.94</v>
+        <v>1631.25</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1908.08</v>
+        <v>1928.54</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>10859.45</v>
+        <v>10975.93</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1135.34</v>
+        <v>1147.52</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>17789.1</v>
+        <v>17979.92</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1868.12</v>
+        <v>1888.16</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>6231.96</v>
+        <v>6298.81</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>773.98</v>
+        <v>782.28</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1022.15</v>
+        <v>1033.11</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>939.34</v>
+        <v>949.41</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2856.46</v>
+        <v>2887.1</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>762.63</v>
+        <v>770.8099999999999</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>18767.48</v>
+        <v>18998.13</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1889.92</v>
+        <v>1913.15</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3601.98</v>
+        <v>3646.25</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5943.26</v>
+        <v>6016.3</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>5896.99</v>
+        <v>5969.46</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>779.34</v>
+        <v>788.92</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>13364.95</v>
+        <v>13529.2</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>32113.2</v>
+        <v>32507.87</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>37797.86</v>
+        <v>38262.4</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4839.97</v>
+        <v>4899.45</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>10822.82</v>
+        <v>10955.83</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>4507.17</v>
+        <v>4562.56</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>5707.15</v>
+        <v>5780.49</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5015.97</v>
+        <v>5080.42</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>823.5</v>
+        <v>834.08</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2105.47</v>
+        <v>2132.53</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>5956.38</v>
+        <v>6032.91</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1476.58</v>
+        <v>1495.56</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>20594.35</v>
+        <v>20858.98</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1309.25</v>
+        <v>1326.07</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2013.29</v>
+        <v>2039.16</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2256.32</v>
+        <v>2285.31</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>872.83</v>
+        <v>884.05</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>8105.32</v>
+        <v>8209.469999999999</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3026.85</v>
+        <v>3065.75</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>18216.92</v>
+        <v>18451</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6865.73</v>
+        <v>6953.96</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>18669.73</v>
+        <v>18909.63</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1354.09</v>
+        <v>1371.49</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4760.32</v>
+        <v>4821.49</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1495</v>
+        <v>1514.21</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1334.37</v>
+        <v>1351.51</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>8171.8</v>
+        <v>8276.809999999999</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>5026.73</v>
+        <v>5054.22</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1405.1</v>
+        <v>1412.79</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>19045.19</v>
+        <v>19149.34</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>12208.76</v>
+        <v>12275.52</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>3952.68</v>
+        <v>3974.3</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1144.8</v>
+        <v>1151.06</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>14144.46</v>
+        <v>14221.81</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>6032.07</v>
+        <v>6065.06</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>98716.06</v>
+        <v>99255.91</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>74986.03</v>
+        <v>75396.11</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>3100.22</v>
+        <v>3117.18</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2215.48</v>
+        <v>2227.6</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>872.84</v>
+        <v>877.61</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>10798.07</v>
+        <v>10857.12</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1605.14</v>
+        <v>1613.92</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>9209.809999999999</v>
+        <v>9260.18</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>565279.3199999999</v>
+        <v>568370.6800000001</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>867.3200000000001</v>
+        <v>872.0700000000001</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1173.94</v>
+        <v>1180.36</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>3571.24</v>
+        <v>3590.77</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1501.2</v>
+        <v>1509.41</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3345.31</v>
+        <v>3363.61</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>16133.57</v>
+        <v>16221.8</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>26387.15</v>
+        <v>26531.45</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>920.4400000000001</v>
+        <v>925.47</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2911.78</v>
+        <v>2927.7</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2387.11</v>
+        <v>2400.16</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>2804.5</v>
+        <v>2819.83</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>14368.29</v>
+        <v>14446.87</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>18222.09</v>
+        <v>18321.74</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>893.51</v>
+        <v>898.4</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>6582.35</v>
+        <v>6618.34</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>9962.59</v>
+        <v>10017.07</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3046.12</v>
+        <v>3062.78</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>29150.1</v>
+        <v>29309.51</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1135.26</v>
+        <v>1141.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN-SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MULTINEGOCIOS R&amp;G</t>
+          <t>Multinegocios R&amp;G</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Universidad de Chile - Bienestar del Personal</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dirección de Vialidad - Región XVI - Punilla</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>MULTINEGOCIOS R&amp;G</t>
+          <t>Multinegocios R&amp;G</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOVAL PLUSS SPA </t>
+          <t xml:space="preserve">Moval Pluss Spa </t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Museo Marítimo Nacional</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
+          <t>Importadora y Comercializadora Proinmin SpA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22199,12 +22199,12 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25013,7 +25013,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25023,7 +25023,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
@@ -745,7 +745,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2180,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2306,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2371,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2436,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2562,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2810,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2875,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3001,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3066,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3192,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3318,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3383,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3509,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3879,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3944,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4009,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4135,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4200,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4631,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4757,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4883,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4948,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5074,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5200,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5265,11 @@
           <t>77.103.803-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5391,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5700,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5887,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5952,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6261,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6326,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6391,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6456,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6643,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6769,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6895,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7021,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7208,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7273,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7399,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7525,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8017,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8143,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8208,11 @@
           <t>77.414.534-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8273,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8338,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8647,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8773,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8899,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8964,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9334,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9399,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9708,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9895,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10448,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10513,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10578,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10704,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10956,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11021,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11086,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11212,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11338,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11403,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11773,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12204,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12391,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12700,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12765,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12830,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12895,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13021,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13147,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13212,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13338,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13525,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13590,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13838,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13903,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14090,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14460,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14525,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14590,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14838,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14903,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14968,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15033,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15098,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15163,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15228,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15354,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15663,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15850,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15915,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16163,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16533,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16598,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16663,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16728,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16976,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17041,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17228,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17415,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17724,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18460,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18708,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18773,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +18960,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19269,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19334,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19460,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19586,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19834,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20082,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20330,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20395,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20460,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20586,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20651,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21387,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21513,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +21822,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +21948,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22135,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22261,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22387,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22513,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22822,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23253,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23318,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23505,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23570,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23635,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23883,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24070,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24135,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24387,11 @@
           <t>76.156.939-2</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +24635,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +24948,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25013,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +25261,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24726,7 +25326,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +25452,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +25517,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +25582,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +25891,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +25956,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/dic-2025.xlsx
@@ -3131,7 +3131,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6078,7 +6082,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9212,7 +9220,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
